--- a/artfynd/A 35643-2023 artfynd.xlsx
+++ b/artfynd/A 35643-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 35643-2023 artfynd.xlsx
+++ b/artfynd/A 35643-2023 artfynd.xlsx
@@ -799,12 +799,7 @@
         <v>550056</v>
       </c>
       <c r="B3" t="n">
-        <v>104789</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107210</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>419091.7922344111</v>
+        <v>419092</v>
       </c>
       <c r="R3" t="n">
-        <v>6412771.030453998</v>
+        <v>6412771</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -869,19 +864,9 @@
           <t>1992-08-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1992-08-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1037,12 +1022,7 @@
         <v>2570073</v>
       </c>
       <c r="B5" t="n">
-        <v>106963</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109398</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>419091.7922344111</v>
+        <v>419092</v>
       </c>
       <c r="R5" t="n">
-        <v>6412771.030453998</v>
+        <v>6412771</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1107,19 +1087,9 @@
           <t>1992-08-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1992-08-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">

--- a/artfynd/A 35643-2023 artfynd.xlsx
+++ b/artfynd/A 35643-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>3332104</v>
       </c>
       <c r="B2" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>419091.7922344111</v>
+        <v>419092</v>
       </c>
       <c r="R2" t="n">
-        <v>6412771.030453998</v>
+        <v>6412771</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1992-08-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1992-08-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -905,12 +890,7 @@
         <v>6445939</v>
       </c>
       <c r="B4" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102801</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>419091.7922344111</v>
+        <v>419092</v>
       </c>
       <c r="R4" t="n">
-        <v>6412771.030453998</v>
+        <v>6412771</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -971,19 +951,9 @@
           <t>1992-08-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1992-08-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 35643-2023 artfynd.xlsx
+++ b/artfynd/A 35643-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3332104</v>
       </c>
       <c r="B2" t="n">
-        <v>106169</v>
+        <v>106181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>550056</v>
       </c>
       <c r="B3" t="n">
-        <v>107210</v>
+        <v>107224</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>6445939</v>
       </c>
       <c r="B4" t="n">
-        <v>102801</v>
+        <v>102812</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>2570073</v>
       </c>
       <c r="B5" t="n">
-        <v>109398</v>
+        <v>109413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35643-2023 artfynd.xlsx
+++ b/artfynd/A 35643-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3332104</v>
       </c>
       <c r="B2" t="n">
-        <v>106181</v>
+        <v>106190</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>550056</v>
       </c>
       <c r="B3" t="n">
-        <v>107224</v>
+        <v>107233</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>6445939</v>
       </c>
       <c r="B4" t="n">
-        <v>102812</v>
+        <v>102820</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>2570073</v>
       </c>
       <c r="B5" t="n">
-        <v>109413</v>
+        <v>109422</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35643-2023 artfynd.xlsx
+++ b/artfynd/A 35643-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3332104</v>
       </c>
       <c r="B2" t="n">
-        <v>106190</v>
+        <v>106202</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>550056</v>
       </c>
       <c r="B3" t="n">
-        <v>107233</v>
+        <v>107245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>6445939</v>
       </c>
       <c r="B4" t="n">
-        <v>102820</v>
+        <v>102830</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>2570073</v>
       </c>
       <c r="B5" t="n">
-        <v>109422</v>
+        <v>109435</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35643-2023 artfynd.xlsx
+++ b/artfynd/A 35643-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3332104</v>
       </c>
       <c r="B2" t="n">
-        <v>106202</v>
+        <v>106211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>550056</v>
       </c>
       <c r="B3" t="n">
-        <v>107245</v>
+        <v>107254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>6445939</v>
       </c>
       <c r="B4" t="n">
-        <v>102830</v>
+        <v>102836</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>2570073</v>
       </c>
       <c r="B5" t="n">
-        <v>109435</v>
+        <v>109444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35643-2023 artfynd.xlsx
+++ b/artfynd/A 35643-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3332104</v>
       </c>
       <c r="B2" t="n">
-        <v>106211</v>
+        <v>106216</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>550056</v>
       </c>
       <c r="B3" t="n">
-        <v>107254</v>
+        <v>107259</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>6445939</v>
       </c>
       <c r="B4" t="n">
-        <v>102836</v>
+        <v>102837</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>2570073</v>
       </c>
       <c r="B5" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35643-2023 artfynd.xlsx
+++ b/artfynd/A 35643-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3332104</v>
       </c>
       <c r="B2" t="n">
-        <v>106216</v>
+        <v>106244</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>550056</v>
       </c>
       <c r="B3" t="n">
-        <v>107259</v>
+        <v>107287</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>6445939</v>
       </c>
       <c r="B4" t="n">
-        <v>102837</v>
+        <v>102864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>2570073</v>
       </c>
       <c r="B5" t="n">
-        <v>109449</v>
+        <v>109477</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35643-2023 artfynd.xlsx
+++ b/artfynd/A 35643-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3332104</v>
       </c>
       <c r="B2" t="n">
-        <v>106244</v>
+        <v>106250</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>550056</v>
       </c>
       <c r="B3" t="n">
-        <v>107287</v>
+        <v>107293</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>6445939</v>
       </c>
       <c r="B4" t="n">
-        <v>102864</v>
+        <v>102870</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>2570073</v>
       </c>
       <c r="B5" t="n">
-        <v>109477</v>
+        <v>109483</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35643-2023 artfynd.xlsx
+++ b/artfynd/A 35643-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3332104</v>
       </c>
       <c r="B2" t="n">
-        <v>106250</v>
+        <v>106257</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>550056</v>
       </c>
       <c r="B3" t="n">
-        <v>107293</v>
+        <v>107300</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>6445939</v>
       </c>
       <c r="B4" t="n">
-        <v>102870</v>
+        <v>102877</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>2570073</v>
       </c>
       <c r="B5" t="n">
-        <v>109483</v>
+        <v>109490</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35643-2023 artfynd.xlsx
+++ b/artfynd/A 35643-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3332104</v>
       </c>
       <c r="B2" t="n">
-        <v>106257</v>
+        <v>106261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>550056</v>
       </c>
       <c r="B3" t="n">
-        <v>107300</v>
+        <v>107304</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>6445939</v>
       </c>
       <c r="B4" t="n">
-        <v>102877</v>
+        <v>102881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>2570073</v>
       </c>
       <c r="B5" t="n">
-        <v>109490</v>
+        <v>109494</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35643-2023 artfynd.xlsx
+++ b/artfynd/A 35643-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3332104</v>
       </c>
       <c r="B2" t="n">
-        <v>106261</v>
+        <v>106268</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>550056</v>
       </c>
       <c r="B3" t="n">
-        <v>107304</v>
+        <v>107312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>6445939</v>
       </c>
       <c r="B4" t="n">
-        <v>102881</v>
+        <v>102888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>2570073</v>
       </c>
       <c r="B5" t="n">
-        <v>109494</v>
+        <v>109502</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35643-2023 artfynd.xlsx
+++ b/artfynd/A 35643-2023 artfynd.xlsx
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3332104</v>
+        <v>550056</v>
       </c>
       <c r="B2" t="n">
-        <v>106271</v>
+        <v>107868</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>1855</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Åkerkulla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Anthemis arvensis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>550056</v>
+        <v>2570073</v>
       </c>
       <c r="B3" t="n">
-        <v>107315</v>
+        <v>110078</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,16 +792,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1855</v>
+        <v>220299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Åkerkulla</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anthemis arvensis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -887,30 +887,34 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6445939</v>
+        <v>3332104</v>
       </c>
       <c r="B4" t="n">
-        <v>102891</v>
+        <v>106813</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>225046</v>
+        <v>220785</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -989,34 +993,30 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2570073</v>
+        <v>6445939</v>
       </c>
       <c r="B5" t="n">
-        <v>109505</v>
+        <v>103404</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>225046</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Vanlig skogsalm</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>

--- a/artfynd/A 35643-2023 artfynd.xlsx
+++ b/artfynd/A 35643-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Västergötlands flora 2002</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/550056</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Västergötlands flora 2002</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2570073</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
           <t>Västergötlands flora 2002</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3332104</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,8 +1112,19 @@
           <t>Västergötlands flora 2002</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6445939</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>